--- a/Proiect/Proiect/Output/Date/Date_Proiect_Final_2023.xlsx
+++ b/Proiect/Proiect/Output/Date/Date_Proiect_Final_2023.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -775,933 +775,1123 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Finlanda</t>
-        </is>
-      </c>
       <c r="B9">
         <v>2023</v>
       </c>
       <c r="C9">
-        <v>126722</v>
+        <v>9699</v>
       </c>
       <c r="D9">
-        <v>43280</v>
+        <v>21210</v>
       </c>
       <c r="E9">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="F9">
-        <v>73236</v>
-      </c>
-      <c r="G9">
-        <v>7759</v>
+        <v>26399</v>
       </c>
       <c r="H9">
-        <v>18.4</v>
+        <v>31.8</v>
       </c>
       <c r="I9">
         <v>1</v>
       </c>
       <c r="J9">
-        <v>11.74975098975199</v>
+        <v>9.179778066393542</v>
       </c>
       <c r="K9">
-        <v>10.67544591352036</v>
+        <v>9.962228047558728</v>
       </c>
       <c r="L9">
-        <v>5.318119993844216</v>
+        <v>3.871201010907891</v>
       </c>
       <c r="M9">
-        <v>11.20145603672614</v>
-      </c>
-      <c r="N9">
-        <v>8.95660873889395</v>
+        <v>10.18111928913441</v>
       </c>
       <c r="O9">
-        <v>2.91235066461494</v>
+        <v>3.459466289786131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Germania</t>
+          <t>Finlanda</t>
         </is>
       </c>
       <c r="B10">
         <v>2023</v>
       </c>
       <c r="C10">
-        <v>1172337</v>
+        <v>126722</v>
       </c>
       <c r="D10">
-        <v>43450</v>
+        <v>43280</v>
       </c>
       <c r="E10">
-        <v>1342</v>
+        <v>204</v>
       </c>
       <c r="F10">
-        <v>1303251</v>
+        <v>73236</v>
       </c>
       <c r="G10">
-        <v>263466</v>
+        <v>7759</v>
       </c>
       <c r="H10">
-        <v>235.8</v>
+        <v>18.4</v>
       </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10">
-        <v>13.97450975044874</v>
+        <v>11.74975098975199</v>
       </c>
       <c r="K10">
-        <v>10.67936613069354</v>
+        <v>10.67544591352036</v>
       </c>
       <c r="L10">
-        <v>7.201916317531627</v>
+        <v>5.318119993844216</v>
       </c>
       <c r="M10">
-        <v>14.08037323725415</v>
+        <v>11.20145603672614</v>
       </c>
       <c r="N10">
-        <v>12.48167960638011</v>
+        <v>8.95660873889395</v>
       </c>
       <c r="O10">
-        <v>5.462983988103271</v>
+        <v>2.91235066461494</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Grecia</t>
-        </is>
-      </c>
       <c r="B11">
         <v>2023</v>
       </c>
       <c r="C11">
-        <v>68659</v>
+        <v>1359102</v>
       </c>
       <c r="D11">
-        <v>18600</v>
+        <v>37760</v>
       </c>
       <c r="E11">
-        <v>522</v>
+        <v>2263</v>
       </c>
       <c r="F11">
-        <v>118816</v>
-      </c>
-      <c r="G11">
-        <v>56548</v>
+        <v>417613</v>
       </c>
       <c r="H11">
-        <v>80</v>
+        <v>107.9</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>11.13690750238479</v>
+        <v>14.12233474550442</v>
       </c>
       <c r="K11">
-        <v>9.830916859701293</v>
+        <v>10.53900562025944</v>
       </c>
       <c r="L11">
-        <v>6.257667587882639</v>
+        <v>7.724446645633537</v>
       </c>
       <c r="M11">
-        <v>11.68533977331629</v>
-      </c>
-      <c r="N11">
-        <v>10.94284511398692</v>
+        <v>12.94231283989283</v>
       </c>
       <c r="O11">
-        <v>4.382026634673881</v>
+        <v>4.681204872264089</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ungaria</t>
+          <t>Germania</t>
         </is>
       </c>
       <c r="B12">
         <v>2023</v>
       </c>
       <c r="C12">
-        <v>50934</v>
+        <v>1172337</v>
       </c>
       <c r="D12">
-        <v>16050</v>
+        <v>43450</v>
       </c>
       <c r="E12">
-        <v>201</v>
+        <v>1342</v>
       </c>
       <c r="F12">
-        <v>96192</v>
+        <v>1303251</v>
       </c>
       <c r="G12">
-        <v>36219</v>
+        <v>263466</v>
       </c>
       <c r="H12">
-        <v>105.1</v>
+        <v>235.8</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>10.83828595596602</v>
+        <v>13.97450975044874</v>
       </c>
       <c r="K12">
-        <v>9.683464128558162</v>
+        <v>10.67936613069354</v>
       </c>
       <c r="L12">
-        <v>5.303304908059076</v>
+        <v>7.201916317531627</v>
       </c>
       <c r="M12">
-        <v>11.47411186893353</v>
+        <v>14.08037323725415</v>
       </c>
       <c r="N12">
-        <v>10.4973391220005</v>
+        <v>12.48167960638011</v>
       </c>
       <c r="O12">
-        <v>4.654912277882906</v>
+        <v>5.462983988103271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Islanda</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B13">
         <v>2023</v>
       </c>
       <c r="C13">
-        <v>3629</v>
+        <v>68659</v>
       </c>
       <c r="D13">
-        <v>61180</v>
+        <v>18600</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>522</v>
       </c>
       <c r="F13">
-        <v>11235</v>
+        <v>118816</v>
       </c>
       <c r="G13">
-        <v>783</v>
+        <v>56548</v>
       </c>
       <c r="H13">
-        <v>3.8</v>
+        <v>80</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>8.19671240721307</v>
+        <v>11.13690750238479</v>
       </c>
       <c r="K13">
-        <v>11.02157561770489</v>
+        <v>9.830916859701293</v>
       </c>
       <c r="L13">
-        <v>2.079441541679836</v>
+        <v>6.257667587882639</v>
       </c>
       <c r="M13">
-        <v>9.326878188224134</v>
+        <v>11.68533977331629</v>
       </c>
       <c r="N13">
-        <v>6.663132695990803</v>
+        <v>10.94284511398692</v>
       </c>
       <c r="O13">
-        <v>1.33500106673234</v>
+        <v>4.382026634673881</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Ungaria</t>
         </is>
       </c>
       <c r="B14">
         <v>2023</v>
       </c>
       <c r="C14">
-        <v>69354</v>
+        <v>50934</v>
       </c>
       <c r="D14">
-        <v>87810</v>
+        <v>16050</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="F14">
-        <v>135617</v>
+        <v>96192</v>
       </c>
       <c r="G14">
-        <v>17643</v>
+        <v>36219</v>
       </c>
       <c r="H14">
-        <v>77.40000000000001</v>
+        <v>105.1</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14">
-        <v>11.14697910252232</v>
+        <v>10.83828595596602</v>
       </c>
       <c r="K14">
-        <v>11.38293066835404</v>
+        <v>9.683464128558162</v>
       </c>
       <c r="L14">
-        <v>4.787491742782046</v>
+        <v>5.303304908059076</v>
       </c>
       <c r="M14">
-        <v>11.81759738904164</v>
+        <v>11.47411186893353</v>
       </c>
       <c r="N14">
-        <v>9.778094383128066</v>
+        <v>10.4973391220005</v>
       </c>
       <c r="O14">
-        <v>4.348986780595681</v>
+        <v>4.654912277882906</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Letonia</t>
+          <t>Islanda</t>
         </is>
       </c>
       <c r="B15">
         <v>2023</v>
       </c>
       <c r="C15">
-        <v>10712</v>
+        <v>3629</v>
       </c>
       <c r="D15">
-        <v>16770</v>
+        <v>61180</v>
       </c>
       <c r="E15">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>18710</v>
+        <v>11235</v>
       </c>
       <c r="G15">
-        <v>4055</v>
+        <v>783</v>
       </c>
       <c r="H15">
-        <v>30.2</v>
+        <v>3.8</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>9.279119887371008</v>
+        <v>8.19671240721307</v>
       </c>
       <c r="K15">
-        <v>9.727346854817254</v>
+        <v>11.02157561770489</v>
       </c>
       <c r="L15">
-        <v>4.127134385045092</v>
+        <v>2.079441541679836</v>
       </c>
       <c r="M15">
-        <v>9.836866865194231</v>
+        <v>9.326878188224134</v>
       </c>
       <c r="N15">
-        <v>8.307705966549513</v>
+        <v>6.663132695990803</v>
       </c>
       <c r="O15">
-        <v>3.407841924380824</v>
+        <v>1.33500106673234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lituania</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B16">
         <v>2023</v>
       </c>
       <c r="C16">
-        <v>10094</v>
+        <v>69354</v>
       </c>
       <c r="D16">
-        <v>19220</v>
+        <v>87810</v>
       </c>
       <c r="E16">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F16">
-        <v>66682</v>
+        <v>135617</v>
       </c>
       <c r="G16">
-        <v>7495</v>
+        <v>17643</v>
       </c>
       <c r="H16">
-        <v>45.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16">
-        <v>9.219696466900208</v>
+        <v>11.14697910252232</v>
       </c>
       <c r="K16">
-        <v>9.863706682524283</v>
+        <v>11.38293066835404</v>
       </c>
       <c r="L16">
-        <v>4.663439094112067</v>
+        <v>4.787491742782046</v>
       </c>
       <c r="M16">
-        <v>11.10770532685446</v>
+        <v>11.81759738904164</v>
       </c>
       <c r="N16">
-        <v>8.921991410536698</v>
+        <v>9.778094383128066</v>
       </c>
       <c r="O16">
-        <v>3.824284091120139</v>
+        <v>4.348986780595681</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Luxemburg</t>
-        </is>
-      </c>
       <c r="B17">
         <v>2023</v>
       </c>
       <c r="C17">
-        <v>22268</v>
+        <v>888340</v>
       </c>
       <c r="D17">
-        <v>102250</v>
+        <v>32640</v>
       </c>
       <c r="E17">
-        <v>18</v>
+        <v>1947</v>
       </c>
       <c r="F17">
-        <v>26964</v>
-      </c>
-      <c r="G17">
-        <v>3111</v>
+        <v>439658</v>
       </c>
       <c r="H17">
-        <v>257.7</v>
+        <v>198.1</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17">
-        <v>10.0109059493034</v>
+        <v>13.69710983157624</v>
       </c>
       <c r="K17">
-        <v>11.53517607390505</v>
+        <v>10.39329380907804</v>
       </c>
       <c r="L17">
-        <v>2.890371757896165</v>
+        <v>7.574045005372199</v>
       </c>
       <c r="M17">
-        <v>10.20229500777133</v>
-      </c>
-      <c r="N17">
-        <v>8.042699496897637</v>
+        <v>12.99375470542669</v>
       </c>
       <c r="O17">
-        <v>5.551796117658319</v>
+        <v>5.288771953704505</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B18">
         <v>2023</v>
       </c>
       <c r="C18">
-        <v>3716</v>
+        <v>10712</v>
       </c>
       <c r="D18">
-        <v>33380</v>
+        <v>16770</v>
       </c>
       <c r="E18">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F18">
-        <v>42239</v>
+        <v>18710</v>
       </c>
       <c r="G18">
-        <v>2125</v>
+        <v>4055</v>
       </c>
       <c r="H18">
-        <v>1766</v>
+        <v>30.2</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="J18">
-        <v>8.22040309993373</v>
+        <v>9.279119887371008</v>
       </c>
       <c r="K18">
-        <v>10.41571219721583</v>
+        <v>9.727346854817254</v>
       </c>
       <c r="L18">
-        <v>2.397895272798371</v>
+        <v>4.127134385045092</v>
       </c>
       <c r="M18">
-        <v>10.65112291838014</v>
+        <v>9.836866865194231</v>
       </c>
       <c r="N18">
-        <v>7.661527081358517</v>
+        <v>8.307705966549513</v>
       </c>
       <c r="O18">
-        <v>7.476472381163905</v>
+        <v>3.407841924380824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olanda</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B19">
         <v>2023</v>
       </c>
       <c r="C19">
-        <v>245460</v>
+        <v>10094</v>
       </c>
       <c r="D19">
-        <v>50660</v>
+        <v>19220</v>
       </c>
       <c r="E19">
-        <v>359</v>
+        <v>106</v>
       </c>
       <c r="F19">
-        <v>274597</v>
+        <v>66682</v>
       </c>
       <c r="G19">
-        <v>50940</v>
+        <v>7495</v>
       </c>
       <c r="H19">
-        <v>526</v>
+        <v>45.8</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
       <c r="J19">
-        <v>12.4108892801515</v>
+        <v>9.219696466900208</v>
       </c>
       <c r="K19">
-        <v>10.83289192355567</v>
+        <v>9.863706682524283</v>
       </c>
       <c r="L19">
-        <v>5.883322388488279</v>
+        <v>4.663439094112067</v>
       </c>
       <c r="M19">
-        <v>12.52306348896829</v>
+        <v>11.10770532685446</v>
       </c>
       <c r="N19">
-        <v>10.83840374853345</v>
+        <v>8.921991410536698</v>
       </c>
       <c r="O19">
-        <v>6.26530121273771</v>
+        <v>3.824284091120139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Luxemburg</t>
         </is>
       </c>
       <c r="B20">
         <v>2023</v>
       </c>
       <c r="C20">
-        <v>117183</v>
+        <v>22268</v>
       </c>
       <c r="D20">
-        <v>15950</v>
+        <v>102250</v>
       </c>
       <c r="E20">
-        <v>502</v>
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>303275</v>
+        <v>26964</v>
       </c>
       <c r="G20">
-        <v>96698</v>
+        <v>3111</v>
       </c>
       <c r="H20">
-        <v>119.4</v>
+        <v>257.7</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>11.67149209440957</v>
+        <v>10.0109059493034</v>
       </c>
       <c r="K20">
-        <v>9.67721410821299</v>
+        <v>11.53517607390505</v>
       </c>
       <c r="L20">
-        <v>6.218600119691729</v>
+        <v>2.890371757896165</v>
       </c>
       <c r="M20">
-        <v>12.62239856097108</v>
+        <v>10.20229500777133</v>
       </c>
       <c r="N20">
-        <v>11.47934799870423</v>
+        <v>8.042699496897637</v>
       </c>
       <c r="O20">
-        <v>4.782479200958502</v>
+        <v>5.551796117658319</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portugalia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B21">
         <v>2023</v>
       </c>
       <c r="C21">
-        <v>75123</v>
+        <v>3716</v>
       </c>
       <c r="D21">
-        <v>22130</v>
+        <v>33380</v>
       </c>
       <c r="E21">
-        <v>351</v>
+        <v>11</v>
       </c>
       <c r="F21">
-        <v>189367</v>
+        <v>42239</v>
       </c>
       <c r="G21">
-        <v>46292</v>
+        <v>2125</v>
       </c>
       <c r="H21">
-        <v>116.3</v>
+        <v>1766</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
       <c r="J21">
-        <v>11.22688204918696</v>
+        <v>8.22040309993373</v>
       </c>
       <c r="K21">
-        <v>10.0046894330451</v>
+        <v>10.41571219721583</v>
       </c>
       <c r="L21">
-        <v>5.860786223465865</v>
+        <v>2.397895272798371</v>
       </c>
       <c r="M21">
-        <v>12.15144749086623</v>
+        <v>10.65112291838014</v>
       </c>
       <c r="N21">
-        <v>10.74272443896797</v>
+        <v>7.661527081358517</v>
       </c>
       <c r="O21">
-        <v>4.756173059524619</v>
+        <v>7.476472381163905</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>România</t>
-        </is>
-      </c>
       <c r="B22">
         <v>2023</v>
       </c>
       <c r="C22">
-        <v>63734</v>
+        <v>332</v>
       </c>
       <c r="D22">
-        <v>12970</v>
+        <v>8620</v>
       </c>
       <c r="E22">
-        <v>456</v>
+        <v>48</v>
       </c>
       <c r="F22">
-        <v>324091</v>
-      </c>
-      <c r="G22">
-        <v>50795</v>
+        <v>18316</v>
       </c>
       <c r="H22">
-        <v>81.40000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
       <c r="J22">
-        <v>11.06247345112767</v>
+        <v>5.805134968916488</v>
       </c>
       <c r="K22">
-        <v>9.47039427731049</v>
+        <v>9.061840363657739</v>
       </c>
       <c r="L22">
-        <v>6.122492809514386</v>
+        <v>3.871201010907891</v>
       </c>
       <c r="M22">
-        <v>12.6887827050854</v>
-      </c>
-      <c r="N22">
-        <v>10.83555320352565</v>
+        <v>9.815584869360217</v>
       </c>
       <c r="O22">
-        <v>4.399375273008495</v>
+        <v>3.819907716520341</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Slovacia</t>
+          <t>Olanda</t>
         </is>
       </c>
       <c r="B23">
         <v>2023</v>
       </c>
       <c r="C23">
-        <v>11826</v>
+        <v>245460</v>
       </c>
       <c r="D23">
-        <v>18750</v>
+        <v>50660</v>
       </c>
       <c r="E23">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="F23">
-        <v>5923</v>
+        <v>274597</v>
       </c>
       <c r="G23">
-        <v>20037</v>
+        <v>50940</v>
       </c>
       <c r="H23">
-        <v>111.4</v>
+        <v>526</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23">
-        <v>9.378055776380775</v>
+        <v>12.4108892801515</v>
       </c>
       <c r="K23">
-        <v>9.838949031398556</v>
+        <v>10.83289192355567</v>
       </c>
       <c r="L23">
-        <v>5.087596335232384</v>
+        <v>5.883322388488279</v>
       </c>
       <c r="M23">
-        <v>8.68676717538769</v>
+        <v>12.52306348896829</v>
       </c>
       <c r="N23">
-        <v>9.905335843393745</v>
+        <v>10.83840374853345</v>
       </c>
       <c r="O23">
-        <v>4.713127327493184</v>
+        <v>6.26530121273771</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
       <c r="B24">
         <v>2023</v>
       </c>
       <c r="C24">
-        <v>24895</v>
+        <v>110995</v>
       </c>
       <c r="D24">
-        <v>25120</v>
+        <v>62790</v>
       </c>
       <c r="E24">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="F24">
-        <v>33939</v>
-      </c>
-      <c r="G24">
-        <v>7083</v>
+        <v>86589</v>
       </c>
       <c r="H24">
-        <v>105.3</v>
+        <v>15.2</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>10.12242225907628</v>
+        <v>11.61724043423487</v>
       </c>
       <c r="K24">
-        <v>10.13141962058213</v>
+        <v>11.04755110410816</v>
       </c>
       <c r="L24">
-        <v>3.637586159726386</v>
+        <v>4.672828834461906</v>
       </c>
       <c r="M24">
-        <v>10.43234953878822</v>
-      </c>
-      <c r="N24">
-        <v>8.865452825753623</v>
+        <v>11.36893961444185</v>
       </c>
       <c r="O24">
-        <v>4.65681341913993</v>
+        <v>2.721295427852231</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B25">
         <v>2023</v>
       </c>
       <c r="C25">
-        <v>222334</v>
+        <v>117183</v>
       </c>
       <c r="D25">
-        <v>27150</v>
+        <v>15950</v>
       </c>
       <c r="E25">
-        <v>2937</v>
+        <v>502</v>
       </c>
       <c r="F25">
-        <v>1250991</v>
+        <v>303275</v>
       </c>
       <c r="G25">
-        <v>181781</v>
+        <v>96698</v>
       </c>
       <c r="H25">
-        <v>96.2</v>
+        <v>119.4</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="J25">
-        <v>12.31193603472591</v>
+        <v>11.67149209440957</v>
       </c>
       <c r="K25">
-        <v>10.20913232536208</v>
+        <v>9.67721410821299</v>
       </c>
       <c r="L25">
-        <v>7.98514393119862</v>
+        <v>6.218600119691729</v>
       </c>
       <c r="M25">
-        <v>14.03944739454451</v>
+        <v>12.62239856097108</v>
       </c>
       <c r="N25">
-        <v>12.11055794481287</v>
+        <v>11.47934799870423</v>
       </c>
       <c r="O25">
-        <v>4.566429357671661</v>
+        <v>4.782479200958502</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Suedia</t>
+          <t>Portugalia</t>
         </is>
       </c>
       <c r="B26">
         <v>2023</v>
       </c>
       <c r="C26">
-        <v>287940</v>
+        <v>75123</v>
       </c>
       <c r="D26">
-        <v>47960</v>
+        <v>22130</v>
       </c>
       <c r="E26">
-        <v>440</v>
+        <v>351</v>
       </c>
       <c r="F26">
-        <v>94514</v>
+        <v>189367</v>
       </c>
       <c r="G26">
-        <v>22980</v>
+        <v>46292</v>
       </c>
       <c r="H26">
-        <v>25.9</v>
+        <v>116.3</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="J26">
-        <v>12.57050740408035</v>
+        <v>11.22688204918696</v>
       </c>
       <c r="K26">
-        <v>10.77812260914145</v>
+        <v>10.0046894330451</v>
       </c>
       <c r="L26">
-        <v>6.086774726912306</v>
+        <v>5.860786223465865</v>
       </c>
       <c r="M26">
-        <v>11.45651383104427</v>
+        <v>12.15144749086623</v>
       </c>
       <c r="N26">
-        <v>10.04237955140275</v>
+        <v>10.74272443896797</v>
       </c>
       <c r="O26">
-        <v>3.254242968705492</v>
+        <v>4.756173059524619</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>România</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2023</v>
+      </c>
+      <c r="C27">
+        <v>63734</v>
+      </c>
+      <c r="D27">
+        <v>12970</v>
+      </c>
+      <c r="E27">
+        <v>456</v>
+      </c>
+      <c r="F27">
+        <v>324091</v>
+      </c>
+      <c r="G27">
+        <v>50795</v>
+      </c>
+      <c r="H27">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>11.06247345112767</v>
+      </c>
+      <c r="K27">
+        <v>9.47039427731049</v>
+      </c>
+      <c r="L27">
+        <v>6.122492809514386</v>
+      </c>
+      <c r="M27">
+        <v>12.6887827050854</v>
+      </c>
+      <c r="N27">
+        <v>10.83555320352565</v>
+      </c>
+      <c r="O27">
+        <v>4.399375273008495</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Slovacia</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2023</v>
+      </c>
+      <c r="C28">
+        <v>11826</v>
+      </c>
+      <c r="D28">
+        <v>18750</v>
+      </c>
+      <c r="E28">
+        <v>162</v>
+      </c>
+      <c r="F28">
+        <v>5923</v>
+      </c>
+      <c r="G28">
+        <v>20037</v>
+      </c>
+      <c r="H28">
+        <v>111.4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>9.378055776380775</v>
+      </c>
+      <c r="K28">
+        <v>9.838949031398556</v>
+      </c>
+      <c r="L28">
+        <v>5.087596335232384</v>
+      </c>
+      <c r="M28">
+        <v>8.68676717538769</v>
+      </c>
+      <c r="N28">
+        <v>9.905335843393745</v>
+      </c>
+      <c r="O28">
+        <v>4.713127327493184</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2023</v>
+      </c>
+      <c r="C29">
+        <v>24895</v>
+      </c>
+      <c r="D29">
+        <v>25120</v>
+      </c>
+      <c r="E29">
+        <v>38</v>
+      </c>
+      <c r="F29">
+        <v>33939</v>
+      </c>
+      <c r="G29">
+        <v>7083</v>
+      </c>
+      <c r="H29">
+        <v>105.3</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>10.12242225907628</v>
+      </c>
+      <c r="K29">
+        <v>10.13141962058213</v>
+      </c>
+      <c r="L29">
+        <v>3.637586159726386</v>
+      </c>
+      <c r="M29">
+        <v>10.43234953878822</v>
+      </c>
+      <c r="N29">
+        <v>8.865452825753623</v>
+      </c>
+      <c r="O29">
+        <v>4.65681341913993</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2023</v>
+      </c>
+      <c r="C30">
+        <v>222334</v>
+      </c>
+      <c r="D30">
+        <v>27150</v>
+      </c>
+      <c r="E30">
+        <v>2937</v>
+      </c>
+      <c r="F30">
+        <v>1250991</v>
+      </c>
+      <c r="G30">
+        <v>181781</v>
+      </c>
+      <c r="H30">
+        <v>96.2</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>12.31193603472591</v>
+      </c>
+      <c r="K30">
+        <v>10.20913232536208</v>
+      </c>
+      <c r="L30">
+        <v>7.98514393119862</v>
+      </c>
+      <c r="M30">
+        <v>14.03944739454451</v>
+      </c>
+      <c r="N30">
+        <v>12.11055794481287</v>
+      </c>
+      <c r="O30">
+        <v>4.566429357671661</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Suedia</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2023</v>
+      </c>
+      <c r="C31">
+        <v>287940</v>
+      </c>
+      <c r="D31">
+        <v>47960</v>
+      </c>
+      <c r="E31">
+        <v>440</v>
+      </c>
+      <c r="F31">
+        <v>94514</v>
+      </c>
+      <c r="G31">
+        <v>22980</v>
+      </c>
+      <c r="H31">
+        <v>25.9</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>12.57050740408035</v>
+      </c>
+      <c r="K31">
+        <v>10.77812260914145</v>
+      </c>
+      <c r="L31">
+        <v>6.086774726912306</v>
+      </c>
+      <c r="M31">
+        <v>11.45651383104427</v>
+      </c>
+      <c r="N31">
+        <v>10.04237955140275</v>
+      </c>
+      <c r="O31">
+        <v>3.254242968705492</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Elveția</t>
         </is>
       </c>
-      <c r="B27">
-        <v>2023</v>
-      </c>
-      <c r="C27">
+      <c r="B32">
+        <v>2023</v>
+      </c>
+      <c r="C32">
         <v>168575</v>
       </c>
-      <c r="D27">
+      <c r="D32">
         <v>82440</v>
       </c>
-      <c r="E27">
+      <c r="E32">
         <v>204</v>
       </c>
-      <c r="F27">
+      <c r="F32">
         <v>263081</v>
       </c>
-      <c r="G27">
+      <c r="G32">
         <v>18821</v>
       </c>
-      <c r="H27">
+      <c r="H32">
         <v>223</v>
       </c>
-      <c r="I27">
+      <c r="I32">
         <v>0</v>
       </c>
-      <c r="J27">
+      <c r="J32">
         <v>12.03513603360278</v>
       </c>
-      <c r="K27">
+      <c r="K32">
         <v>11.31982603500439</v>
       </c>
-      <c r="L27">
+      <c r="L32">
         <v>5.318119993844216</v>
       </c>
-      <c r="M27">
+      <c r="M32">
         <v>12.48022104963666</v>
       </c>
-      <c r="N27">
+      <c r="N32">
         <v>9.842728546690564</v>
       </c>
-      <c r="O27">
+      <c r="O32">
         <v>5.407171771460119</v>
       </c>
     </row>

--- a/Proiect/Proiect/Output/Date/Date_Proiect_Final_2023.xlsx
+++ b/Proiect/Proiect/Output/Date/Date_Proiect_Final_2023.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,478 +387,415 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Politie</t>
+          <t>Densitate_Populatie</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Densitate_Populatie</t>
+          <t>Est_Vest</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Membru_UE</t>
+          <t>ln_Furturi</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>ln_Furturi</t>
+          <t>ln_PIB</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>ln_PIB</t>
+          <t>ln_Someri</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ln_Someri</t>
+          <t>ln_Imigratie</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ln_Imigratie</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ln_Politie</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>ln_Densitate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
       <c r="B2">
         <v>2023</v>
       </c>
       <c r="C2">
-        <v>110359</v>
+        <v>2334</v>
       </c>
       <c r="D2">
-        <v>45670</v>
+        <v>5500</v>
       </c>
       <c r="E2">
-        <v>241</v>
+        <v>497.4285714285714</v>
       </c>
       <c r="F2">
-        <v>147591</v>
+        <v>203644.0857142857</v>
       </c>
       <c r="G2">
-        <v>31995</v>
+        <v>98.8</v>
       </c>
       <c r="H2">
-        <v>110.7</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>7.755338812846501</v>
       </c>
       <c r="J2">
-        <v>11.61149396703609</v>
+        <v>8.612503371220562</v>
       </c>
       <c r="K2">
-        <v>10.72919690617904</v>
+        <v>6.209451971272821</v>
       </c>
       <c r="L2">
-        <v>5.484796933490655</v>
+        <v>12.22413398174826</v>
       </c>
       <c r="M2">
-        <v>11.9022069891376</v>
-      </c>
-      <c r="N2">
-        <v>10.37333491957356</v>
-      </c>
-      <c r="O2">
-        <v>4.706823839714591</v>
+        <v>4.593097604753822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B3">
         <v>2023</v>
       </c>
       <c r="C3">
-        <v>205003</v>
+        <v>110359</v>
       </c>
       <c r="D3">
-        <v>44230</v>
+        <v>45670</v>
       </c>
       <c r="E3">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="F3">
-        <v>169609</v>
+        <v>147591</v>
       </c>
       <c r="G3">
-        <v>39440</v>
+        <v>110.7</v>
       </c>
       <c r="H3">
-        <v>386.8</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>11.61149396703609</v>
       </c>
       <c r="J3">
-        <v>12.23077989215981</v>
+        <v>10.72919690617904</v>
       </c>
       <c r="K3">
-        <v>10.69715857086237</v>
+        <v>5.484796933490655</v>
       </c>
       <c r="L3">
-        <v>5.683579767338681</v>
+        <v>11.9022069891376</v>
       </c>
       <c r="M3">
-        <v>12.04125696286589</v>
-      </c>
-      <c r="N3">
-        <v>10.58253580871657</v>
-      </c>
-      <c r="O3">
-        <v>5.957907763579139</v>
+        <v>4.706823839714591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="B4">
         <v>2023</v>
       </c>
       <c r="C4">
-        <v>26153</v>
+        <v>205003</v>
       </c>
       <c r="D4">
-        <v>10950</v>
+        <v>44230</v>
       </c>
       <c r="E4">
-        <v>132</v>
+        <v>294</v>
       </c>
       <c r="F4">
-        <v>56807</v>
+        <v>169609</v>
       </c>
       <c r="G4">
-        <v>29120</v>
+        <v>386.8</v>
       </c>
       <c r="H4">
-        <v>58.6</v>
+        <v>0</v>
       </c>
       <c r="I4">
+        <v>12.23077989215981</v>
+      </c>
+      <c r="J4">
+        <v>10.69715857086237</v>
+      </c>
+      <c r="K4">
+        <v>5.683579767338681</v>
+      </c>
+      <c r="L4">
+        <v>12.04125696286589</v>
+      </c>
+      <c r="M4">
+        <v>5.957907763579139</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5">
+        <v>2023</v>
+      </c>
+      <c r="C5">
+        <v>2900</v>
+      </c>
+      <c r="D5">
+        <v>33208.57142857143</v>
+      </c>
+      <c r="E5">
+        <v>181</v>
+      </c>
+      <c r="F5">
+        <v>203644.0857142857</v>
+      </c>
+      <c r="G5">
+        <v>171.2675675675676</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>10.17171918566626</v>
-      </c>
-      <c r="K4">
-        <v>9.301094735244646</v>
-      </c>
-      <c r="L4">
-        <v>4.882801922586371</v>
-      </c>
-      <c r="M4">
-        <v>10.94743243986193</v>
-      </c>
-      <c r="N4">
-        <v>10.27918050231062</v>
-      </c>
-      <c r="O4">
-        <v>4.070734696582967</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Croația</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>2023</v>
-      </c>
-      <c r="C5">
-        <v>11270</v>
-      </c>
-      <c r="D5">
-        <v>16490</v>
-      </c>
-      <c r="E5">
-        <v>106</v>
-      </c>
-      <c r="F5">
-        <v>69396</v>
-      </c>
-      <c r="G5">
-        <v>20333</v>
-      </c>
-      <c r="H5">
-        <v>69</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>7.972466015974566</v>
       </c>
       <c r="J5">
-        <v>9.329899607033822</v>
+        <v>10.41056329714239</v>
       </c>
       <c r="K5">
-        <v>9.710509415553645</v>
+        <v>5.198497031265826</v>
       </c>
       <c r="L5">
-        <v>4.663439094112067</v>
+        <v>12.22413398174826</v>
       </c>
       <c r="M5">
-        <v>11.14759891789485</v>
-      </c>
-      <c r="N5">
-        <v>9.920000460910341</v>
-      </c>
-      <c r="O5">
-        <v>4.23410650459726</v>
+        <v>5.143227056217083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cipru</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B6">
         <v>2023</v>
       </c>
       <c r="C6">
-        <v>776</v>
+        <v>26153</v>
       </c>
       <c r="D6">
-        <v>29200</v>
+        <v>10950</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="F6">
-        <v>40761</v>
+        <v>56807</v>
       </c>
       <c r="G6">
-        <v>5371</v>
+        <v>58.6</v>
       </c>
       <c r="H6">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>10.17171918566626</v>
       </c>
       <c r="J6">
-        <v>6.654152520183219</v>
+        <v>9.301094735244646</v>
       </c>
       <c r="K6">
-        <v>10.28192398825637</v>
+        <v>4.882801922586371</v>
       </c>
       <c r="L6">
-        <v>3.401197381662155</v>
+        <v>10.94743243986193</v>
       </c>
       <c r="M6">
-        <v>10.61550555384632</v>
-      </c>
-      <c r="N6">
-        <v>8.58876938990546</v>
-      </c>
-      <c r="O6">
-        <v>4.644390899141372</v>
+        <v>4.070734696582967</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cehia</t>
+          <t>Croația</t>
         </is>
       </c>
       <c r="B7">
         <v>2023</v>
       </c>
       <c r="C7">
-        <v>35373</v>
+        <v>11270</v>
       </c>
       <c r="D7">
-        <v>21680</v>
+        <v>16490</v>
       </c>
       <c r="E7">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="F7">
-        <v>142149</v>
+        <v>69396</v>
       </c>
       <c r="G7">
-        <v>39306</v>
+        <v>69</v>
       </c>
       <c r="H7">
-        <v>140.7</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>9.329899607033822</v>
       </c>
       <c r="J7">
-        <v>10.47370409624478</v>
+        <v>9.710509415553645</v>
       </c>
       <c r="K7">
-        <v>9.984145455553582</v>
+        <v>4.663439094112067</v>
       </c>
       <c r="L7">
-        <v>4.897839799950911</v>
+        <v>11.14759891789485</v>
       </c>
       <c r="M7">
-        <v>11.86463811707915</v>
-      </c>
-      <c r="N7">
-        <v>10.57913245795993</v>
-      </c>
-      <c r="O7">
-        <v>4.946629964120343</v>
+        <v>4.23410650459726</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danemarca</t>
+          <t>Cipru</t>
         </is>
       </c>
       <c r="B8">
         <v>2023</v>
       </c>
       <c r="C8">
-        <v>158491</v>
+        <v>776</v>
       </c>
       <c r="D8">
-        <v>56470</v>
+        <v>29200</v>
       </c>
       <c r="E8">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>98344</v>
+        <v>40761</v>
       </c>
       <c r="G8">
-        <v>11422</v>
+        <v>104</v>
       </c>
       <c r="H8">
-        <v>141.6</v>
+        <v>0</v>
       </c>
       <c r="I8">
+        <v>6.654152520183219</v>
+      </c>
+      <c r="J8">
+        <v>10.28192398825637</v>
+      </c>
+      <c r="K8">
+        <v>3.401197381662155</v>
+      </c>
+      <c r="L8">
+        <v>10.61550555384632</v>
+      </c>
+      <c r="M8">
+        <v>4.644390899141372</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cehia</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2023</v>
+      </c>
+      <c r="C9">
+        <v>35373</v>
+      </c>
+      <c r="D9">
+        <v>21680</v>
+      </c>
+      <c r="E9">
+        <v>134</v>
+      </c>
+      <c r="F9">
+        <v>142149</v>
+      </c>
+      <c r="G9">
+        <v>140.7</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
-      <c r="J8">
-        <v>11.97345308835291</v>
-      </c>
-      <c r="K8">
-        <v>10.94146480266688</v>
-      </c>
-      <c r="L8">
-        <v>5.087596335232384</v>
-      </c>
-      <c r="M8">
-        <v>11.49623698368399</v>
-      </c>
-      <c r="N8">
-        <v>9.343296599224809</v>
-      </c>
-      <c r="O8">
-        <v>4.953006181259619</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9">
-        <v>2023</v>
-      </c>
-      <c r="C9">
-        <v>9699</v>
-      </c>
-      <c r="D9">
-        <v>21210</v>
-      </c>
-      <c r="E9">
-        <v>48</v>
-      </c>
-      <c r="F9">
-        <v>26399</v>
-      </c>
-      <c r="H9">
-        <v>31.8</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>10.47370409624478</v>
       </c>
       <c r="J9">
-        <v>9.179778066393542</v>
+        <v>9.984145455553582</v>
       </c>
       <c r="K9">
-        <v>9.962228047558728</v>
+        <v>4.897839799950911</v>
       </c>
       <c r="L9">
-        <v>3.871201010907891</v>
+        <v>11.86463811707915</v>
       </c>
       <c r="M9">
-        <v>10.18111928913441</v>
-      </c>
-      <c r="O9">
-        <v>3.459466289786131</v>
+        <v>4.946629964120343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finlanda</t>
+          <t>Danemarca</t>
         </is>
       </c>
       <c r="B10">
         <v>2023</v>
       </c>
       <c r="C10">
-        <v>126722</v>
+        <v>158491</v>
       </c>
       <c r="D10">
-        <v>43280</v>
+        <v>56470</v>
       </c>
       <c r="E10">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="F10">
-        <v>73236</v>
+        <v>98344</v>
       </c>
       <c r="G10">
-        <v>7759</v>
+        <v>141.6</v>
       </c>
       <c r="H10">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>11.97345308835291</v>
       </c>
       <c r="J10">
-        <v>11.74975098975199</v>
+        <v>10.94146480266688</v>
       </c>
       <c r="K10">
-        <v>10.67544591352036</v>
+        <v>5.087596335232384</v>
       </c>
       <c r="L10">
-        <v>5.318119993844216</v>
+        <v>11.49623698368399</v>
       </c>
       <c r="M10">
-        <v>11.20145603672614</v>
-      </c>
-      <c r="N10">
-        <v>8.95660873889395</v>
-      </c>
-      <c r="O10">
-        <v>2.91235066461494</v>
+        <v>4.953006181259619</v>
       </c>
     </row>
     <row r="11">
@@ -866,516 +803,452 @@
         <v>2023</v>
       </c>
       <c r="C11">
-        <v>1359102</v>
+        <v>9699</v>
       </c>
       <c r="D11">
-        <v>37760</v>
+        <v>21210</v>
       </c>
       <c r="E11">
-        <v>2263</v>
+        <v>48</v>
       </c>
       <c r="F11">
-        <v>417613</v>
+        <v>26399</v>
+      </c>
+      <c r="G11">
+        <v>31.8</v>
       </c>
       <c r="H11">
-        <v>107.9</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>9.179778066393542</v>
       </c>
       <c r="J11">
-        <v>14.12233474550442</v>
+        <v>9.962228047558728</v>
       </c>
       <c r="K11">
-        <v>10.53900562025944</v>
+        <v>3.871201010907891</v>
       </c>
       <c r="L11">
-        <v>7.724446645633537</v>
+        <v>10.18111928913441</v>
       </c>
       <c r="M11">
-        <v>12.94231283989283</v>
-      </c>
-      <c r="O11">
-        <v>4.681204872264089</v>
+        <v>3.459466289786131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Germania</t>
+          <t>Finlanda</t>
         </is>
       </c>
       <c r="B12">
         <v>2023</v>
       </c>
       <c r="C12">
-        <v>1172337</v>
+        <v>126722</v>
       </c>
       <c r="D12">
-        <v>43450</v>
+        <v>43280</v>
       </c>
       <c r="E12">
-        <v>1342</v>
+        <v>204</v>
       </c>
       <c r="F12">
-        <v>1303251</v>
+        <v>73236</v>
       </c>
       <c r="G12">
-        <v>263466</v>
+        <v>18.4</v>
       </c>
       <c r="H12">
-        <v>235.8</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>11.74975098975199</v>
       </c>
       <c r="J12">
-        <v>13.97450975044874</v>
+        <v>10.67544591352036</v>
       </c>
       <c r="K12">
-        <v>10.67936613069354</v>
+        <v>5.318119993844216</v>
       </c>
       <c r="L12">
-        <v>7.201916317531627</v>
+        <v>11.20145603672614</v>
       </c>
       <c r="M12">
-        <v>14.08037323725415</v>
-      </c>
-      <c r="N12">
-        <v>12.48167960638011</v>
-      </c>
-      <c r="O12">
-        <v>5.462983988103271</v>
+        <v>2.91235066461494</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Grecia</t>
-        </is>
-      </c>
       <c r="B13">
         <v>2023</v>
       </c>
       <c r="C13">
-        <v>68659</v>
+        <v>1359102</v>
       </c>
       <c r="D13">
-        <v>18600</v>
+        <v>37760</v>
       </c>
       <c r="E13">
-        <v>522</v>
+        <v>2263</v>
       </c>
       <c r="F13">
-        <v>118816</v>
+        <v>417613</v>
       </c>
       <c r="G13">
-        <v>56548</v>
+        <v>107.9</v>
       </c>
       <c r="H13">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>14.12233474550442</v>
       </c>
       <c r="J13">
-        <v>11.13690750238479</v>
+        <v>10.53900562025944</v>
       </c>
       <c r="K13">
-        <v>9.830916859701293</v>
+        <v>7.724446645633537</v>
       </c>
       <c r="L13">
-        <v>6.257667587882639</v>
+        <v>12.94231283989283</v>
       </c>
       <c r="M13">
-        <v>11.68533977331629</v>
-      </c>
-      <c r="N13">
-        <v>10.94284511398692</v>
-      </c>
-      <c r="O13">
-        <v>4.382026634673881</v>
+        <v>4.681204872264089</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ungaria</t>
+          <t>Germania</t>
         </is>
       </c>
       <c r="B14">
         <v>2023</v>
       </c>
       <c r="C14">
-        <v>50934</v>
+        <v>1172337</v>
       </c>
       <c r="D14">
-        <v>16050</v>
+        <v>43450</v>
       </c>
       <c r="E14">
-        <v>201</v>
+        <v>1342</v>
       </c>
       <c r="F14">
-        <v>96192</v>
+        <v>1303251</v>
       </c>
       <c r="G14">
-        <v>36219</v>
+        <v>235.8</v>
       </c>
       <c r="H14">
-        <v>105.1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>13.97450975044874</v>
       </c>
       <c r="J14">
-        <v>10.83828595596602</v>
+        <v>10.67936613069354</v>
       </c>
       <c r="K14">
-        <v>9.683464128558162</v>
+        <v>7.201916317531627</v>
       </c>
       <c r="L14">
-        <v>5.303304908059076</v>
+        <v>14.08037323725415</v>
       </c>
       <c r="M14">
-        <v>11.47411186893353</v>
-      </c>
-      <c r="N14">
-        <v>10.4973391220005</v>
-      </c>
-      <c r="O14">
-        <v>4.654912277882906</v>
+        <v>5.462983988103271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Islanda</t>
+          <t>Grecia</t>
         </is>
       </c>
       <c r="B15">
         <v>2023</v>
       </c>
       <c r="C15">
-        <v>3629</v>
+        <v>68659</v>
       </c>
       <c r="D15">
-        <v>61180</v>
+        <v>18600</v>
       </c>
       <c r="E15">
-        <v>8</v>
+        <v>522</v>
       </c>
       <c r="F15">
-        <v>11235</v>
+        <v>118816</v>
       </c>
       <c r="G15">
-        <v>783</v>
+        <v>80</v>
       </c>
       <c r="H15">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>11.13690750238479</v>
       </c>
       <c r="J15">
-        <v>8.19671240721307</v>
+        <v>9.830916859701293</v>
       </c>
       <c r="K15">
-        <v>11.02157561770489</v>
+        <v>6.257667587882639</v>
       </c>
       <c r="L15">
-        <v>2.079441541679836</v>
+        <v>11.68533977331629</v>
       </c>
       <c r="M15">
-        <v>9.326878188224134</v>
-      </c>
-      <c r="N15">
-        <v>6.663132695990803</v>
-      </c>
-      <c r="O15">
-        <v>1.33500106673234</v>
+        <v>4.382026634673881</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>Ungaria</t>
         </is>
       </c>
       <c r="B16">
         <v>2023</v>
       </c>
       <c r="C16">
-        <v>69354</v>
+        <v>50934</v>
       </c>
       <c r="D16">
-        <v>87810</v>
+        <v>16050</v>
       </c>
       <c r="E16">
-        <v>120</v>
+        <v>201</v>
       </c>
       <c r="F16">
-        <v>135617</v>
+        <v>96192</v>
       </c>
       <c r="G16">
-        <v>17643</v>
+        <v>105.1</v>
       </c>
       <c r="H16">
-        <v>77.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>10.83828595596602</v>
       </c>
       <c r="J16">
-        <v>11.14697910252232</v>
+        <v>9.683464128558162</v>
       </c>
       <c r="K16">
-        <v>11.38293066835404</v>
+        <v>5.303304908059076</v>
       </c>
       <c r="L16">
-        <v>4.787491742782046</v>
+        <v>11.47411186893353</v>
       </c>
       <c r="M16">
-        <v>11.81759738904164</v>
-      </c>
-      <c r="N16">
-        <v>9.778094383128066</v>
-      </c>
-      <c r="O16">
-        <v>4.348986780595681</v>
+        <v>4.654912277882906</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Islanda</t>
+        </is>
+      </c>
       <c r="B17">
         <v>2023</v>
       </c>
       <c r="C17">
-        <v>888340</v>
+        <v>3629</v>
       </c>
       <c r="D17">
-        <v>32640</v>
+        <v>61180</v>
       </c>
       <c r="E17">
-        <v>1947</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>439658</v>
+        <v>11235</v>
+      </c>
+      <c r="G17">
+        <v>3.8</v>
       </c>
       <c r="H17">
-        <v>198.1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>8.19671240721307</v>
       </c>
       <c r="J17">
-        <v>13.69710983157624</v>
+        <v>11.02157561770489</v>
       </c>
       <c r="K17">
-        <v>10.39329380907804</v>
+        <v>2.079441541679836</v>
       </c>
       <c r="L17">
-        <v>7.574045005372199</v>
+        <v>9.326878188224134</v>
       </c>
       <c r="M17">
-        <v>12.99375470542669</v>
-      </c>
-      <c r="O17">
-        <v>5.288771953704505</v>
+        <v>1.33500106673234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Letonia</t>
+          <t>Irlanda</t>
         </is>
       </c>
       <c r="B18">
         <v>2023</v>
       </c>
       <c r="C18">
-        <v>10712</v>
+        <v>69354</v>
       </c>
       <c r="D18">
-        <v>16770</v>
+        <v>87810</v>
       </c>
       <c r="E18">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F18">
-        <v>18710</v>
+        <v>135617</v>
       </c>
       <c r="G18">
-        <v>4055</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H18">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>11.14697910252232</v>
       </c>
       <c r="J18">
-        <v>9.279119887371008</v>
+        <v>11.38293066835404</v>
       </c>
       <c r="K18">
-        <v>9.727346854817254</v>
+        <v>4.787491742782046</v>
       </c>
       <c r="L18">
-        <v>4.127134385045092</v>
+        <v>11.81759738904164</v>
       </c>
       <c r="M18">
-        <v>9.836866865194231</v>
-      </c>
-      <c r="N18">
-        <v>8.307705966549513</v>
-      </c>
-      <c r="O18">
-        <v>3.407841924380824</v>
+        <v>4.348986780595681</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Lituania</t>
-        </is>
-      </c>
       <c r="B19">
         <v>2023</v>
       </c>
       <c r="C19">
-        <v>10094</v>
+        <v>888340</v>
       </c>
       <c r="D19">
-        <v>19220</v>
+        <v>32640</v>
       </c>
       <c r="E19">
-        <v>106</v>
+        <v>1947</v>
       </c>
       <c r="F19">
-        <v>66682</v>
+        <v>439658</v>
       </c>
       <c r="G19">
-        <v>7495</v>
+        <v>198.1</v>
       </c>
       <c r="H19">
-        <v>45.8</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>13.69710983157624</v>
       </c>
       <c r="J19">
-        <v>9.219696466900208</v>
+        <v>10.39329380907804</v>
       </c>
       <c r="K19">
-        <v>9.863706682524283</v>
+        <v>7.574045005372199</v>
       </c>
       <c r="L19">
-        <v>4.663439094112067</v>
+        <v>12.99375470542669</v>
       </c>
       <c r="M19">
-        <v>11.10770532685446</v>
-      </c>
-      <c r="N19">
-        <v>8.921991410536698</v>
-      </c>
-      <c r="O19">
-        <v>3.824284091120139</v>
+        <v>5.288771953704505</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Luxemburg</t>
-        </is>
-      </c>
       <c r="B20">
         <v>2023</v>
       </c>
       <c r="C20">
-        <v>22268</v>
+        <v>4621</v>
       </c>
       <c r="D20">
-        <v>102250</v>
+        <v>33208.57142857143</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>497.4285714285714</v>
       </c>
       <c r="F20">
-        <v>26964</v>
+        <v>203644.0857142857</v>
       </c>
       <c r="G20">
-        <v>3111</v>
+        <v>171.2675675675676</v>
       </c>
       <c r="H20">
-        <v>257.7</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>8.438366410870266</v>
       </c>
       <c r="J20">
-        <v>10.0109059493034</v>
+        <v>10.41056329714239</v>
       </c>
       <c r="K20">
-        <v>11.53517607390505</v>
+        <v>6.209451971272821</v>
       </c>
       <c r="L20">
-        <v>2.890371757896165</v>
+        <v>12.22413398174826</v>
       </c>
       <c r="M20">
-        <v>10.20229500777133</v>
-      </c>
-      <c r="N20">
-        <v>8.042699496897637</v>
-      </c>
-      <c r="O20">
-        <v>5.551796117658319</v>
+        <v>5.143227056217083</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Letonia</t>
         </is>
       </c>
       <c r="B21">
         <v>2023</v>
       </c>
       <c r="C21">
-        <v>3716</v>
+        <v>10712</v>
       </c>
       <c r="D21">
-        <v>33380</v>
+        <v>16770</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F21">
-        <v>42239</v>
+        <v>18710</v>
       </c>
       <c r="G21">
-        <v>2125</v>
+        <v>30.2</v>
       </c>
       <c r="H21">
-        <v>1766</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>9.279119887371008</v>
       </c>
       <c r="J21">
-        <v>8.22040309993373</v>
+        <v>9.727346854817254</v>
       </c>
       <c r="K21">
-        <v>10.41571219721583</v>
+        <v>4.127134385045092</v>
       </c>
       <c r="L21">
-        <v>2.397895272798371</v>
+        <v>9.836866865194231</v>
       </c>
       <c r="M21">
-        <v>10.65112291838014</v>
-      </c>
-      <c r="N21">
-        <v>7.661527081358517</v>
-      </c>
-      <c r="O21">
-        <v>7.476472381163905</v>
+        <v>3.407841924380824</v>
       </c>
     </row>
     <row r="22">
@@ -1383,516 +1256,819 @@
         <v>2023</v>
       </c>
       <c r="C22">
-        <v>332</v>
+        <v>245</v>
       </c>
       <c r="D22">
-        <v>8620</v>
+        <v>33208.57142857143</v>
       </c>
       <c r="E22">
-        <v>48</v>
+        <v>497.4285714285714</v>
       </c>
       <c r="F22">
-        <v>18316</v>
+        <v>716</v>
+      </c>
+      <c r="G22">
+        <v>252.2</v>
       </c>
       <c r="H22">
-        <v>45.6</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>5.501258210544727</v>
       </c>
       <c r="J22">
-        <v>5.805134968916488</v>
+        <v>10.41056329714239</v>
       </c>
       <c r="K22">
-        <v>9.061840363657739</v>
+        <v>6.209451971272821</v>
       </c>
       <c r="L22">
-        <v>3.871201010907891</v>
+        <v>6.57507584059962</v>
       </c>
       <c r="M22">
-        <v>9.815584869360217</v>
-      </c>
-      <c r="O22">
-        <v>3.819907716520341</v>
+        <v>5.530222423530819</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Olanda</t>
+          <t>Lituania</t>
         </is>
       </c>
       <c r="B23">
         <v>2023</v>
       </c>
       <c r="C23">
-        <v>245460</v>
+        <v>10094</v>
       </c>
       <c r="D23">
-        <v>50660</v>
+        <v>19220</v>
       </c>
       <c r="E23">
-        <v>359</v>
+        <v>106</v>
       </c>
       <c r="F23">
-        <v>274597</v>
+        <v>66682</v>
       </c>
       <c r="G23">
-        <v>50940</v>
+        <v>45.8</v>
       </c>
       <c r="H23">
-        <v>526</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>9.219696466900208</v>
       </c>
       <c r="J23">
-        <v>12.4108892801515</v>
+        <v>9.863706682524283</v>
       </c>
       <c r="K23">
-        <v>10.83289192355567</v>
+        <v>4.663439094112067</v>
       </c>
       <c r="L23">
-        <v>5.883322388488279</v>
+        <v>11.10770532685446</v>
       </c>
       <c r="M23">
-        <v>12.52306348896829</v>
-      </c>
-      <c r="N23">
-        <v>10.83840374853345</v>
-      </c>
-      <c r="O23">
-        <v>6.26530121273771</v>
+        <v>3.824284091120139</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Luxemburg</t>
+        </is>
+      </c>
       <c r="B24">
         <v>2023</v>
       </c>
       <c r="C24">
-        <v>110995</v>
+        <v>22268</v>
       </c>
       <c r="D24">
-        <v>62790</v>
+        <v>102250</v>
       </c>
       <c r="E24">
-        <v>107</v>
+        <v>18</v>
       </c>
       <c r="F24">
-        <v>86589</v>
+        <v>26964</v>
+      </c>
+      <c r="G24">
+        <v>257.7</v>
       </c>
       <c r="H24">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>10.0109059493034</v>
       </c>
       <c r="J24">
-        <v>11.61724043423487</v>
+        <v>11.53517607390505</v>
       </c>
       <c r="K24">
-        <v>11.04755110410816</v>
+        <v>2.890371757896165</v>
       </c>
       <c r="L24">
-        <v>4.672828834461906</v>
+        <v>10.20229500777133</v>
       </c>
       <c r="M24">
-        <v>11.36893961444185</v>
-      </c>
-      <c r="O24">
-        <v>2.721295427852231</v>
+        <v>5.551796117658319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Polonia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B25">
         <v>2023</v>
       </c>
       <c r="C25">
-        <v>117183</v>
+        <v>3716</v>
       </c>
       <c r="D25">
-        <v>15950</v>
+        <v>33380</v>
       </c>
       <c r="E25">
-        <v>502</v>
+        <v>11</v>
       </c>
       <c r="F25">
-        <v>303275</v>
+        <v>42239</v>
       </c>
       <c r="G25">
-        <v>96698</v>
+        <v>1766</v>
       </c>
       <c r="H25">
-        <v>119.4</v>
+        <v>0</v>
       </c>
       <c r="I25">
+        <v>8.22040309993373</v>
+      </c>
+      <c r="J25">
+        <v>10.41571219721583</v>
+      </c>
+      <c r="K25">
+        <v>2.397895272798371</v>
+      </c>
+      <c r="L25">
+        <v>10.65112291838014</v>
+      </c>
+      <c r="M25">
+        <v>7.476472381163905</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26">
+        <v>2023</v>
+      </c>
+      <c r="C26">
+        <v>158862.3513513514</v>
+      </c>
+      <c r="D26">
+        <v>33208.57142857143</v>
+      </c>
+      <c r="E26">
+        <v>497.4285714285714</v>
+      </c>
+      <c r="F26">
+        <v>97517</v>
+      </c>
+      <c r="G26">
+        <v>171.2675675675676</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>11.97579339148355</v>
+      </c>
+      <c r="J26">
+        <v>10.41056329714239</v>
+      </c>
+      <c r="K26">
+        <v>6.209451971272821</v>
+      </c>
+      <c r="L26">
+        <v>11.48779225533123</v>
+      </c>
+      <c r="M26">
+        <v>5.143227056217083</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27">
+        <v>2023</v>
+      </c>
+      <c r="C27">
+        <v>332</v>
+      </c>
+      <c r="D27">
+        <v>8620</v>
+      </c>
+      <c r="E27">
+        <v>48</v>
+      </c>
+      <c r="F27">
+        <v>18316</v>
+      </c>
+      <c r="G27">
+        <v>45.6</v>
+      </c>
+      <c r="H27">
         <v>1</v>
       </c>
-      <c r="J25">
-        <v>11.67149209440957</v>
-      </c>
-      <c r="K25">
-        <v>9.67721410821299</v>
-      </c>
-      <c r="L25">
-        <v>6.218600119691729</v>
-      </c>
-      <c r="M25">
-        <v>12.62239856097108</v>
-      </c>
-      <c r="N25">
-        <v>11.47934799870423</v>
-      </c>
-      <c r="O25">
-        <v>4.782479200958502</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Portugalia</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>2023</v>
-      </c>
-      <c r="C26">
-        <v>75123</v>
-      </c>
-      <c r="D26">
-        <v>22130</v>
-      </c>
-      <c r="E26">
-        <v>351</v>
-      </c>
-      <c r="F26">
-        <v>189367</v>
-      </c>
-      <c r="G26">
-        <v>46292</v>
-      </c>
-      <c r="H26">
-        <v>116.3</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>11.22688204918696</v>
-      </c>
-      <c r="K26">
-        <v>10.0046894330451</v>
-      </c>
-      <c r="L26">
-        <v>5.860786223465865</v>
-      </c>
-      <c r="M26">
-        <v>12.15144749086623</v>
-      </c>
-      <c r="N26">
-        <v>10.74272443896797</v>
-      </c>
-      <c r="O26">
-        <v>4.756173059524619</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>România</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>2023</v>
-      </c>
-      <c r="C27">
-        <v>63734</v>
-      </c>
-      <c r="D27">
-        <v>12970</v>
-      </c>
-      <c r="E27">
-        <v>456</v>
-      </c>
-      <c r="F27">
-        <v>324091</v>
-      </c>
-      <c r="G27">
-        <v>50795</v>
-      </c>
-      <c r="H27">
-        <v>81.40000000000001</v>
-      </c>
       <c r="I27">
-        <v>1</v>
+        <v>5.805134968916488</v>
       </c>
       <c r="J27">
-        <v>11.06247345112767</v>
+        <v>9.061840363657739</v>
       </c>
       <c r="K27">
-        <v>9.47039427731049</v>
+        <v>3.871201010907891</v>
       </c>
       <c r="L27">
-        <v>6.122492809514386</v>
+        <v>9.815584869360217</v>
       </c>
       <c r="M27">
-        <v>12.6887827050854</v>
-      </c>
-      <c r="N27">
-        <v>10.83555320352565</v>
-      </c>
-      <c r="O27">
-        <v>4.399375273008495</v>
+        <v>3.819907716520341</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Slovacia</t>
+          <t>Olanda</t>
         </is>
       </c>
       <c r="B28">
         <v>2023</v>
       </c>
       <c r="C28">
-        <v>11826</v>
+        <v>245460</v>
       </c>
       <c r="D28">
-        <v>18750</v>
+        <v>50660</v>
       </c>
       <c r="E28">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="F28">
-        <v>5923</v>
+        <v>274597</v>
       </c>
       <c r="G28">
-        <v>20037</v>
+        <v>526</v>
       </c>
       <c r="H28">
-        <v>111.4</v>
+        <v>0</v>
       </c>
       <c r="I28">
+        <v>12.4108892801515</v>
+      </c>
+      <c r="J28">
+        <v>10.83289192355567</v>
+      </c>
+      <c r="K28">
+        <v>5.883322388488279</v>
+      </c>
+      <c r="L28">
+        <v>12.52306348896829</v>
+      </c>
+      <c r="M28">
+        <v>6.26530121273771</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29">
+        <v>2023</v>
+      </c>
+      <c r="C29">
+        <v>158862.3513513514</v>
+      </c>
+      <c r="D29">
+        <v>6540</v>
+      </c>
+      <c r="E29">
+        <v>104</v>
+      </c>
+      <c r="F29">
+        <v>2452</v>
+      </c>
+      <c r="G29">
+        <v>73.7</v>
+      </c>
+      <c r="H29">
         <v>1</v>
       </c>
-      <c r="J28">
-        <v>9.378055776380775</v>
-      </c>
-      <c r="K28">
-        <v>9.838949031398556</v>
-      </c>
-      <c r="L28">
-        <v>5.087596335232384</v>
-      </c>
-      <c r="M28">
-        <v>8.68676717538769</v>
-      </c>
-      <c r="N28">
-        <v>9.905335843393745</v>
-      </c>
-      <c r="O28">
-        <v>4.713127327493184</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>2023</v>
-      </c>
-      <c r="C29">
-        <v>24895</v>
-      </c>
-      <c r="D29">
-        <v>25120</v>
-      </c>
-      <c r="E29">
-        <v>38</v>
-      </c>
-      <c r="F29">
-        <v>33939</v>
-      </c>
-      <c r="G29">
-        <v>7083</v>
-      </c>
-      <c r="H29">
-        <v>105.3</v>
-      </c>
       <c r="I29">
-        <v>1</v>
+        <v>11.97579339148355</v>
       </c>
       <c r="J29">
-        <v>10.12242225907628</v>
+        <v>8.785692444451245</v>
       </c>
       <c r="K29">
-        <v>10.13141962058213</v>
+        <v>4.644390899141372</v>
       </c>
       <c r="L29">
-        <v>3.637586159726386</v>
+        <v>7.80506704425849</v>
       </c>
       <c r="M29">
-        <v>10.43234953878822</v>
-      </c>
-      <c r="N29">
-        <v>8.865452825753623</v>
-      </c>
-      <c r="O29">
-        <v>4.65681341913993</v>
+        <v>4.300002799195291</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
       <c r="B30">
         <v>2023</v>
       </c>
       <c r="C30">
-        <v>222334</v>
+        <v>110995</v>
       </c>
       <c r="D30">
-        <v>27150</v>
+        <v>62790</v>
       </c>
       <c r="E30">
-        <v>2937</v>
+        <v>107</v>
       </c>
       <c r="F30">
-        <v>1250991</v>
+        <v>86589</v>
       </c>
       <c r="G30">
-        <v>181781</v>
+        <v>15.2</v>
       </c>
       <c r="H30">
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>11.61724043423487</v>
       </c>
       <c r="J30">
-        <v>12.31193603472591</v>
+        <v>11.04755110410816</v>
       </c>
       <c r="K30">
-        <v>10.20913232536208</v>
+        <v>4.672828834461906</v>
       </c>
       <c r="L30">
-        <v>7.98514393119862</v>
+        <v>11.36893961444185</v>
       </c>
       <c r="M30">
-        <v>14.03944739454451</v>
-      </c>
-      <c r="N30">
-        <v>12.11055794481287</v>
-      </c>
-      <c r="O30">
-        <v>4.566429357671661</v>
+        <v>2.721295427852231</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Suedia</t>
+          <t>Polonia</t>
         </is>
       </c>
       <c r="B31">
         <v>2023</v>
       </c>
       <c r="C31">
-        <v>287940</v>
+        <v>117183</v>
       </c>
       <c r="D31">
-        <v>47960</v>
+        <v>15950</v>
       </c>
       <c r="E31">
-        <v>440</v>
+        <v>502</v>
       </c>
       <c r="F31">
-        <v>94514</v>
+        <v>303275</v>
       </c>
       <c r="G31">
-        <v>22980</v>
+        <v>119.4</v>
       </c>
       <c r="H31">
-        <v>25.9</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>11.67149209440957</v>
       </c>
       <c r="J31">
-        <v>12.57050740408035</v>
+        <v>9.67721410821299</v>
       </c>
       <c r="K31">
-        <v>10.77812260914145</v>
+        <v>6.218600119691729</v>
       </c>
       <c r="L31">
-        <v>6.086774726912306</v>
+        <v>12.62239856097108</v>
       </c>
       <c r="M31">
-        <v>11.45651383104427</v>
-      </c>
-      <c r="N31">
-        <v>10.04237955140275</v>
-      </c>
-      <c r="O31">
-        <v>3.254242968705492</v>
+        <v>4.782479200958502</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Portugalia</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2023</v>
+      </c>
+      <c r="C32">
+        <v>75123</v>
+      </c>
+      <c r="D32">
+        <v>22130</v>
+      </c>
+      <c r="E32">
+        <v>351</v>
+      </c>
+      <c r="F32">
+        <v>189367</v>
+      </c>
+      <c r="G32">
+        <v>116.3</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>11.22688204918696</v>
+      </c>
+      <c r="J32">
+        <v>10.0046894330451</v>
+      </c>
+      <c r="K32">
+        <v>5.860786223465865</v>
+      </c>
+      <c r="L32">
+        <v>12.15144749086623</v>
+      </c>
+      <c r="M32">
+        <v>4.756173059524619</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>România</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2023</v>
+      </c>
+      <c r="C33">
+        <v>63734</v>
+      </c>
+      <c r="D33">
+        <v>12970</v>
+      </c>
+      <c r="E33">
+        <v>456</v>
+      </c>
+      <c r="F33">
+        <v>324091</v>
+      </c>
+      <c r="G33">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>11.06247345112767</v>
+      </c>
+      <c r="J33">
+        <v>9.47039427731049</v>
+      </c>
+      <c r="K33">
+        <v>6.122492809514386</v>
+      </c>
+      <c r="L33">
+        <v>12.6887827050854</v>
+      </c>
+      <c r="M33">
+        <v>4.399375273008495</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34">
+        <v>2023</v>
+      </c>
+      <c r="C34">
+        <v>14783</v>
+      </c>
+      <c r="D34">
+        <v>8510</v>
+      </c>
+      <c r="E34">
+        <v>296</v>
+      </c>
+      <c r="F34">
+        <v>203644.0857142857</v>
+      </c>
+      <c r="G34">
+        <v>90.5</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>9.60123315090109</v>
+      </c>
+      <c r="J34">
+        <v>9.04899722156742</v>
+      </c>
+      <c r="K34">
+        <v>5.69035945432406</v>
+      </c>
+      <c r="L34">
+        <v>12.22413398174826</v>
+      </c>
+      <c r="M34">
+        <v>4.505349850705881</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Slovacia</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2023</v>
+      </c>
+      <c r="C35">
+        <v>11826</v>
+      </c>
+      <c r="D35">
+        <v>18750</v>
+      </c>
+      <c r="E35">
+        <v>162</v>
+      </c>
+      <c r="F35">
+        <v>5923</v>
+      </c>
+      <c r="G35">
+        <v>111.4</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>9.378055776380775</v>
+      </c>
+      <c r="J35">
+        <v>9.838949031398556</v>
+      </c>
+      <c r="K35">
+        <v>5.087596335232384</v>
+      </c>
+      <c r="L35">
+        <v>8.68676717538769</v>
+      </c>
+      <c r="M35">
+        <v>4.713127327493184</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2023</v>
+      </c>
+      <c r="C36">
+        <v>24895</v>
+      </c>
+      <c r="D36">
+        <v>25120</v>
+      </c>
+      <c r="E36">
+        <v>38</v>
+      </c>
+      <c r="F36">
+        <v>33939</v>
+      </c>
+      <c r="G36">
+        <v>105.3</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>10.12242225907628</v>
+      </c>
+      <c r="J36">
+        <v>10.13141962058213</v>
+      </c>
+      <c r="K36">
+        <v>3.637586159726386</v>
+      </c>
+      <c r="L36">
+        <v>10.43234953878822</v>
+      </c>
+      <c r="M36">
+        <v>4.65681341913993</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>2023</v>
+      </c>
+      <c r="C37">
+        <v>222334</v>
+      </c>
+      <c r="D37">
+        <v>27150</v>
+      </c>
+      <c r="E37">
+        <v>2937</v>
+      </c>
+      <c r="F37">
+        <v>1250991</v>
+      </c>
+      <c r="G37">
+        <v>96.2</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>12.31193603472591</v>
+      </c>
+      <c r="J37">
+        <v>10.20913232536208</v>
+      </c>
+      <c r="K37">
+        <v>7.98514393119862</v>
+      </c>
+      <c r="L37">
+        <v>14.03944739454451</v>
+      </c>
+      <c r="M37">
+        <v>4.566429357671661</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Suedia</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2023</v>
+      </c>
+      <c r="C38">
+        <v>287940</v>
+      </c>
+      <c r="D38">
+        <v>47960</v>
+      </c>
+      <c r="E38">
+        <v>440</v>
+      </c>
+      <c r="F38">
+        <v>94514</v>
+      </c>
+      <c r="G38">
+        <v>25.9</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>12.57050740408035</v>
+      </c>
+      <c r="J38">
+        <v>10.77812260914145</v>
+      </c>
+      <c r="K38">
+        <v>6.086774726912306</v>
+      </c>
+      <c r="L38">
+        <v>11.45651383104427</v>
+      </c>
+      <c r="M38">
+        <v>3.254242968705492</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Elveția</t>
         </is>
       </c>
-      <c r="B32">
-        <v>2023</v>
-      </c>
-      <c r="C32">
+      <c r="B39">
+        <v>2023</v>
+      </c>
+      <c r="C39">
         <v>168575</v>
       </c>
-      <c r="D32">
+      <c r="D39">
         <v>82440</v>
       </c>
-      <c r="E32">
+      <c r="E39">
         <v>204</v>
       </c>
-      <c r="F32">
+      <c r="F39">
         <v>263081</v>
       </c>
-      <c r="G32">
-        <v>18821</v>
-      </c>
-      <c r="H32">
+      <c r="G39">
         <v>223</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>12.03513603360278</v>
       </c>
-      <c r="K32">
+      <c r="J39">
         <v>11.31982603500439</v>
       </c>
-      <c r="L32">
+      <c r="K39">
         <v>5.318119993844216</v>
       </c>
-      <c r="M32">
+      <c r="L39">
         <v>12.48022104963666</v>
       </c>
-      <c r="N32">
-        <v>9.842728546690564</v>
-      </c>
-      <c r="O32">
+      <c r="M39">
         <v>5.407171771460119</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40">
+        <v>2023</v>
+      </c>
+      <c r="C40">
+        <v>181636</v>
+      </c>
+      <c r="D40">
+        <v>8920</v>
+      </c>
+      <c r="E40">
+        <v>3274</v>
+      </c>
+      <c r="F40">
+        <v>203644.0857142857</v>
+      </c>
+      <c r="G40">
+        <v>111.3</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>12.10975996338826</v>
+      </c>
+      <c r="J40">
+        <v>9.096051225574055</v>
+      </c>
+      <c r="K40">
+        <v>8.093767757931079</v>
+      </c>
+      <c r="L40">
+        <v>12.22413398174826</v>
+      </c>
+      <c r="M40">
+        <v>4.712229258281499</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41">
+        <v>2023</v>
+      </c>
+      <c r="C41">
+        <v>158862.3513513514</v>
+      </c>
+      <c r="D41">
+        <v>33208.57142857143</v>
+      </c>
+      <c r="E41">
+        <v>497.4285714285714</v>
+      </c>
+      <c r="F41">
+        <v>680906</v>
+      </c>
+      <c r="G41">
+        <v>275.3</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>11.97579339148355</v>
+      </c>
+      <c r="J41">
+        <v>10.41056329714239</v>
+      </c>
+      <c r="K41">
+        <v>6.209451971272821</v>
+      </c>
+      <c r="L41">
+        <v>13.4311810119293</v>
+      </c>
+      <c r="M41">
+        <v>5.617861412148562</v>
       </c>
     </row>
   </sheetData>
